--- a/models/POWER_UTILITIES.xlsx
+++ b/models/POWER_UTILITIES.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T05:55:08+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-29T18:55:59+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="C2" s="6">
-        <f>'BREN'!$C$148</f>
+        <f>'BREN'!$C$154</f>
         <v/>
       </c>
       <c r="D2" s="7">
-        <f>'BREN'!$C$146</f>
+        <f>'BREN'!$C$152</f>
         <v/>
       </c>
       <c r="E2" s="7">
@@ -1061,18 +1061,18 @@
         <v/>
       </c>
       <c r="F2" s="8">
-        <f>'BREN'!$C$147</f>
+        <f>'BREN'!$C$153</f>
         <v/>
       </c>
       <c r="G2" s="7">
-        <f>'BREN'!$C$127</f>
+        <f>'BREN'!$C$133</f>
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>119.390851</v>
+        <v>119.938334</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>34.441755</v>
+        <v>34.581938</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>0</v>
@@ -1090,11 +1090,11 @@
         </is>
       </c>
       <c r="C3" s="6">
-        <f>'CDIA'!$C$135</f>
+        <f>'CDIA'!$C$147</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>'CDIA'!$C$133</f>
+        <f>'CDIA'!$C$145</f>
         <v/>
       </c>
       <c r="E3" s="7">
@@ -1102,21 +1102,21 @@
         <v/>
       </c>
       <c r="F3" s="8">
-        <f>'CDIA'!$C$134</f>
+        <f>'CDIA'!$C$146</f>
         <v/>
       </c>
       <c r="G3" s="7">
-        <f>'CDIA'!$C$114</f>
+        <f>'CDIA'!$C$126</f>
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>116.172094</v>
+        <v>116.704817</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>77.994136</v>
+        <v>78.31366199999999</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.002152</v>
+        <v>0.002142</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD164"/>
+  <dimension ref="A1:AD170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.1235229700143938</v>
+        <v>0.1229591243062492</v>
       </c>
     </row>
     <row r="92">
@@ -8699,158 +8699,144 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>EV/EBITDA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Weight: DCF to end of life (no terminal value)</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="n">
-        <v>0.999833</v>
+          <t>Target multiple (peer median)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="n">
+        <v>11.510167</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Weight: DCF (FCFF, terminal value)</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>0.000167</v>
+          <t>Metric (LTM, or next-12m DPS for yield)</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="n">
+        <v>526.417</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Value today (weighted)</t>
+          <t>Value per share (IDR) — EV/EBITDA</t>
         </is>
       </c>
       <c r="C127" s="24">
-        <f>$C$109*$C$125+$C$122*$C$126</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>DPS expected in next 12 months (IDR)</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="n">
-        <v>0</v>
+        <f>MAX(0,($C$125*$C$126-($C$79-$C$80)-$C$81+$C$82+$C$83)/$C$77*$C$85*$C$78)</f>
+        <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Base-case 12-month value</t>
-        </is>
-      </c>
-      <c r="C129" s="24">
-        <f>MAX(0,$C$127*(1+$C$94)-$C$128)</f>
-        <v/>
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Bear probability</t>
+          <t>Weight: DCF to end of life (no terminal value)</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>0.25</v>
+        <v>0.666556</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bear 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C131" s="15" t="n">
-        <v>37.61818030511722</v>
+          <t>Weight: DCF (FCFF, terminal value)</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="n">
+        <v>0.000111</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Base probability</t>
+          <t>Weight: EV/EBITDA</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.5</v>
+        <v>0.333333</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Bull probability</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="n">
-        <v>0.25</v>
+          <t>Value today (weighted)</t>
+        </is>
+      </c>
+      <c r="C133" s="24">
+        <f>$C$109*$C$130+$C$122*$C$131+$C$127*$C$132</f>
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Bull 12-month value (engine)</t>
+          <t>DPS expected in next 12 months (IDR)</t>
         </is>
       </c>
       <c r="C134" s="15" t="n">
-        <v>54.91353208586692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Probability-weighted 12-month value</t>
+          <t>Base-case 12-month value</t>
         </is>
       </c>
       <c r="C135" s="24">
-        <f>$C$130*$C$131+$C$132*$C$129+$C$133*$C$134</f>
+        <f>MAX(0,$C$133*(1+$C$94)-$C$134)</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Liquidity discount (limits.yaml)</t>
+          <t>Bear probability</t>
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fundamental 12-month value (after liquidity discount)</t>
-        </is>
-      </c>
-      <c r="C137" s="24">
-        <f>$C$135*(1-$C$136)</f>
-        <v/>
+          <t>Bear 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="n">
+        <v>229.0133708281588</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Konglo lens: price / fundamental value today (engine)</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="n">
-        <v>55.246968</v>
+          <t>Base probability</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Regime bear: probability (konglo deck)</t>
+          <t>Bull probability</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
@@ -8860,353 +8846,415 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Regime bear: share of the log gap closed in 12 months</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="n">
-        <v>0.85</v>
+          <t>Bull 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="n">
+        <v>240.4907830864687</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Regime base: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="n">
-        <v>0.5</v>
+          <t>Probability-weighted 12-month value</t>
+        </is>
+      </c>
+      <c r="C141" s="24">
+        <f>$C$136*$C$137+$C$138*$C$135+$C$139*$C$140</f>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Regime base: share of the log gap closed in 12 months</t>
+          <t>Liquidity discount (limits.yaml)</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Regime bull: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="n">
-        <v>0.25</v>
+          <t>Fundamental 12-month value (after liquidity discount)</t>
+        </is>
+      </c>
+      <c r="C143" s="24">
+        <f>$C$141*(1-$C$142)</f>
+        <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Regime bull: share of the log gap closed in 12 months</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="n">
-        <v>0</v>
+          <t>Konglo lens: price / fundamental value today (engine)</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="n">
+        <v>10.825458</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Share of today's premium kept (probability-weighted)</t>
-        </is>
-      </c>
-      <c r="C145" s="25">
-        <f>$C$139*$C$138^(1-$C$140)+$C$141*$C$138^(1-$C$142)+$C$143*$C$138^(1-$C$144)</f>
-        <v/>
+          <t>Regime bear: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TARGET PRICE (IDR) — konglo lens</t>
-        </is>
-      </c>
-      <c r="C146" s="26">
-        <f>$C$137*$C$145</f>
-        <v/>
+          <t>Regime bear: share of the log gap closed in 12 months</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Expected 12-month total return</t>
-        </is>
-      </c>
-      <c r="C147" s="27">
-        <f>($C$146+$C$128)/$C$76-1</f>
-        <v/>
+          <t>Regime base: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>Regime base: share of the log gap closed in 12 months</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Regime bull: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Regime bull: share of the log gap closed in 12 months</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Share of today's premium kept (probability-weighted)</t>
+        </is>
+      </c>
+      <c r="C151" s="25">
+        <f>$C$145*$C$144^(1-$C$146)+$C$147*$C$144^(1-$C$148)+$C$149*$C$144^(1-$C$150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TARGET PRICE (IDR) — konglo lens</t>
+        </is>
+      </c>
+      <c r="C152" s="26">
+        <f>$C$143*$C$151</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Expected 12-month total return</t>
+        </is>
+      </c>
+      <c r="C153" s="27">
+        <f>($C$152+$C$134)/$C$76-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="C148" s="28">
-        <f>IF($C$147&gt;=0.25,"BUY",IF($C$147&gt;=0.1,"ADD",IF($C$147&lt;=-0.25,"SELL",IF($C$147&lt;=-0.1,"REDUCE","HOLD"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="inlineStr">
+      <c r="C154" s="28">
+        <f>IF($C$153&gt;=0.25,"BUY",IF($C$153&gt;=0.1,"ADD",IF($C$153&lt;=-0.25,"SELL",IF($C$153&lt;=-0.1,"REDUCE","HOLD"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
         <is>
           <t>DCF value per share vs WACC and terminal growth (engine values)</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>rows: Terminal growth (+/- pp) · columns: WACC (+/- pp)</t>
         </is>
       </c>
-      <c r="D151" s="1" t="n">
+      <c r="D157" s="1" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E151" s="1" t="n">
+      <c r="E157" s="1" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F151" s="1" t="n">
+      <c r="F157" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G151" s="1" t="n">
+      <c r="G157" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="H151" s="1" t="n">
+      <c r="H157" s="1" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="152">
-      <c r="C152" s="1" t="n">
+    <row r="158">
+      <c r="C158" s="1" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D152" s="24" t="n">
-        <v>70.2607</v>
-      </c>
-      <c r="E152" s="24" t="n">
-        <v>58.69163</v>
-      </c>
-      <c r="F152" s="24" t="n">
-        <v>47.872918</v>
-      </c>
-      <c r="G152" s="24" t="n">
-        <v>37.723024</v>
-      </c>
-      <c r="H152" s="24" t="n">
-        <v>28.174575</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="C153" s="1" t="n">
+      <c r="D158" s="24" t="n">
+        <v>69.935367</v>
+      </c>
+      <c r="E158" s="24" t="n">
+        <v>58.419413</v>
+      </c>
+      <c r="F158" s="24" t="n">
+        <v>47.650358</v>
+      </c>
+      <c r="G158" s="24" t="n">
+        <v>37.547039</v>
+      </c>
+      <c r="H158" s="24" t="n">
+        <v>28.042397</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="C159" s="1" t="n">
         <v>-0.005</v>
       </c>
-      <c r="D153" s="24" t="n">
-        <v>70.969801</v>
-      </c>
-      <c r="E153" s="24" t="n">
-        <v>59.249061</v>
-      </c>
-      <c r="F153" s="24" t="n">
-        <v>48.31552</v>
-      </c>
-      <c r="G153" s="24" t="n">
-        <v>38.077553</v>
-      </c>
-      <c r="H153" s="24" t="n">
-        <v>28.460781</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="C154" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="24" t="n">
-        <v>71.79686100000001</v>
-      </c>
-      <c r="E154" s="24" t="n">
-        <v>59.892101</v>
-      </c>
-      <c r="F154" s="24" t="n">
-        <v>48.821248</v>
-      </c>
-      <c r="G154" s="24" t="n">
-        <v>38.479281</v>
-      </c>
-      <c r="H154" s="24" t="n">
-        <v>28.782712</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="C155" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D155" s="24" t="n">
-        <v>72.773985</v>
-      </c>
-      <c r="E155" s="24" t="n">
-        <v>60.642112</v>
-      </c>
-      <c r="F155" s="24" t="n">
-        <v>49.404644</v>
-      </c>
-      <c r="G155" s="24" t="n">
-        <v>38.938305</v>
-      </c>
-      <c r="H155" s="24" t="n">
-        <v>29.147501</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="C156" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D156" s="24" t="n">
-        <v>73.94609</v>
-      </c>
-      <c r="E156" s="24" t="n">
-        <v>61.528206</v>
-      </c>
-      <c r="F156" s="24" t="n">
-        <v>50.085088</v>
-      </c>
-      <c r="G156" s="24" t="n">
-        <v>39.467825</v>
-      </c>
-      <c r="H156" s="24" t="n">
-        <v>29.564319</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="inlineStr">
-        <is>
-          <t>12-month value vs revenue growth and gross margin (engine values)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>rows: Gross margin (+/- pp) · columns: Revenue growth (+/- pp, every year)</t>
-        </is>
-      </c>
-      <c r="D159" s="1" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="E159" s="1" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F159" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H159" s="1" t="n">
-        <v>0.04</v>
+      <c r="D159" s="24" t="n">
+        <v>70.641164</v>
+      </c>
+      <c r="E159" s="24" t="n">
+        <v>58.97425</v>
+      </c>
+      <c r="F159" s="24" t="n">
+        <v>48.090901</v>
+      </c>
+      <c r="G159" s="24" t="n">
+        <v>37.89992</v>
+      </c>
+      <c r="H159" s="24" t="n">
+        <v>28.327273</v>
       </c>
     </row>
     <row r="160">
       <c r="C160" s="1" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="D160" s="24" t="n">
-        <v>0</v>
+        <v>71.464367</v>
       </c>
       <c r="E160" s="24" t="n">
-        <v>0.000328</v>
+        <v>59.614294</v>
       </c>
       <c r="F160" s="24" t="n">
-        <v>35.73147</v>
+        <v>48.594275</v>
       </c>
       <c r="G160" s="24" t="n">
-        <v>81.79089</v>
+        <v>38.299779</v>
       </c>
       <c r="H160" s="24" t="n">
-        <v>137.513496</v>
+        <v>28.647707</v>
       </c>
     </row>
     <row r="161">
       <c r="C161" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D161" s="24" t="n">
-        <v>0</v>
+        <v>72.43692799999999</v>
       </c>
       <c r="E161" s="24" t="n">
-        <v>1.741194</v>
+        <v>60.360806</v>
       </c>
       <c r="F161" s="24" t="n">
-        <v>40.692635</v>
+        <v>49.174952</v>
       </c>
       <c r="G161" s="24" t="n">
-        <v>87.536705</v>
+        <v>38.756667</v>
       </c>
       <c r="H161" s="24" t="n">
-        <v>144.210538</v>
+        <v>29.0108</v>
       </c>
     </row>
     <row r="162">
       <c r="C162" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D162" s="24" t="n">
+        <v>73.60355199999999</v>
+      </c>
+      <c r="E162" s="24" t="n">
+        <v>61.242763</v>
+      </c>
+      <c r="F162" s="24" t="n">
+        <v>49.852223</v>
+      </c>
+      <c r="G162" s="24" t="n">
+        <v>39.28372</v>
+      </c>
+      <c r="H162" s="24" t="n">
+        <v>29.425677</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>12-month value vs revenue growth and gross margin (engine values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>rows: Gross margin (+/- pp) · columns: Revenue growth (+/- pp, every year)</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E165" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F165" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D162" s="24" t="n">
+      <c r="G165" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H165" s="1" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="C166" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D166" s="24" t="n">
+        <v>204.052131</v>
+      </c>
+      <c r="E166" s="24" t="n">
+        <v>204.052348</v>
+      </c>
+      <c r="F166" s="24" t="n">
+        <v>227.761402</v>
+      </c>
+      <c r="G166" s="24" t="n">
+        <v>258.326448</v>
+      </c>
+      <c r="H166" s="24" t="n">
+        <v>295.303958</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="C167" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D167" s="24" t="n">
+        <v>204.052131</v>
+      </c>
+      <c r="E167" s="24" t="n">
+        <v>205.20545</v>
+      </c>
+      <c r="F167" s="24" t="n">
+        <v>231.053661</v>
+      </c>
+      <c r="G167" s="24" t="n">
+        <v>262.139402</v>
+      </c>
+      <c r="H167" s="24" t="n">
+        <v>299.748147</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="C168" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E162" s="24" t="n">
-        <v>6.050605</v>
-      </c>
-      <c r="F162" s="24" t="n">
-        <v>45.653801</v>
-      </c>
-      <c r="G162" s="24" t="n">
-        <v>93.28252000000001</v>
-      </c>
-      <c r="H162" s="24" t="n">
-        <v>150.90758</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="C163" s="1" t="n">
+      <c r="D168" s="24" t="n">
+        <v>204.052131</v>
+      </c>
+      <c r="E168" s="24" t="n">
+        <v>208.065203</v>
+      </c>
+      <c r="F168" s="24" t="n">
+        <v>234.345919</v>
+      </c>
+      <c r="G168" s="24" t="n">
+        <v>265.952355</v>
+      </c>
+      <c r="H168" s="24" t="n">
+        <v>304.192336</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="C169" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="D163" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" s="24" t="n">
-        <v>10.360016</v>
-      </c>
-      <c r="F163" s="24" t="n">
-        <v>50.614967</v>
-      </c>
-      <c r="G163" s="24" t="n">
-        <v>99.028335</v>
-      </c>
-      <c r="H163" s="24" t="n">
-        <v>157.604622</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="C164" s="1" t="n">
+      <c r="D169" s="24" t="n">
+        <v>204.052131</v>
+      </c>
+      <c r="E169" s="24" t="n">
+        <v>210.924955</v>
+      </c>
+      <c r="F169" s="24" t="n">
+        <v>237.638178</v>
+      </c>
+      <c r="G169" s="24" t="n">
+        <v>269.765308</v>
+      </c>
+      <c r="H169" s="24" t="n">
+        <v>308.636525</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="C170" s="1" t="n">
         <v>0.02</v>
       </c>
-      <c r="D164" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" s="24" t="n">
-        <v>14.669428</v>
-      </c>
-      <c r="F164" s="24" t="n">
-        <v>55.576132</v>
-      </c>
-      <c r="G164" s="24" t="n">
-        <v>104.774149</v>
-      </c>
-      <c r="H164" s="24" t="n">
-        <v>164.301663</v>
+      <c r="D170" s="24" t="n">
+        <v>204.052131</v>
+      </c>
+      <c r="E170" s="24" t="n">
+        <v>213.784708</v>
+      </c>
+      <c r="F170" s="24" t="n">
+        <v>240.930436</v>
+      </c>
+      <c r="G170" s="24" t="n">
+        <v>273.578262</v>
+      </c>
+      <c r="H170" s="24" t="n">
+        <v>313.080714</v>
       </c>
     </row>
   </sheetData>
@@ -9220,7 +9268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z151"/>
+  <dimension ref="A1:Z163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -14816,7 +14864,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18183</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="79">
@@ -14949,7 +14997,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2567392151010299</v>
+        <v>0.2555672767600858</v>
       </c>
     </row>
     <row r="92">
@@ -15410,504 +15458,600 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>EV/EBITDA</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Weight: DCF (FCFF, terminal value)</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="n">
-        <v>1</v>
+          <t>Target multiple (peer median)</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="n">
+        <v>15.870487</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Value today (weighted)</t>
-        </is>
-      </c>
-      <c r="C114" s="24">
-        <f>$C$110*$C$113</f>
-        <v/>
+          <t>Metric (LTM, or next-12m DPS for yield)</t>
+        </is>
+      </c>
+      <c r="C114" s="13" t="n">
+        <v>17.099855</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DPS expected in next 12 months (IDR)</t>
-        </is>
-      </c>
-      <c r="C115" s="15" t="n">
-        <v>0.9382631905858988</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Base-case 12-month value</t>
-        </is>
-      </c>
-      <c r="C116" s="24">
-        <f>MAX(0,$C$114*(1+$C$94)-$C$115)</f>
+          <t>Value per share (IDR) — EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C115" s="24">
+        <f>MAX(0,($C$113*$C$114-($C$79-$C$80)-$C$81+$C$82+$C$83)/$C$77*$C$85*$C$78)</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Bear probability</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="n">
-        <v>0.25</v>
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Bear 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="n">
-        <v>66.31722365432717</v>
+          <t>Target multiple (peer median)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="n">
+        <v>22.834186</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Base probability</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>0.5</v>
+          <t>Metric (LTM, or next-12m DPS for yield)</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="n">
+        <v>70.49733999999999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bull probability</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Bull 12-month value (engine)</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="n">
-        <v>142.4054475475965</v>
+          <t>Value per share (IDR) — P/E</t>
+        </is>
+      </c>
+      <c r="C120" s="24">
+        <f>MAX(0,$C$118*$C$119/$C$77*$C$85*$C$78)</f>
+        <v/>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Probability-weighted 12-month value</t>
-        </is>
-      </c>
-      <c r="C122" s="24">
-        <f>$C$117*$C$118+$C$119*$C$116+$C$120*$C$121</f>
-        <v/>
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Liquidity discount (limits.yaml)</t>
+          <t>Weight: DCF (FCFF, terminal value)</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Fundamental 12-month value (after liquidity discount)</t>
-        </is>
-      </c>
-      <c r="C124" s="24">
-        <f>$C$122*(1-$C$123)</f>
-        <v/>
+          <t>Weight: EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Konglo lens: price / fundamental value today (engine)</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="n">
-        <v>4.867637</v>
+          <t>Weight: P/E</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Regime bear: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="n">
-        <v>0.25</v>
+          <t>Value today (weighted)</t>
+        </is>
+      </c>
+      <c r="C126" s="24">
+        <f>$C$110*$C$123+$C$115*$C$124+$C$120*$C$125</f>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Regime bear: share of the log gap closed in 12 months</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="n">
-        <v>0.75</v>
+          <t>DPS expected in next 12 months (IDR)</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="n">
+        <v>0.9339802975089242</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Regime base: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>0.5</v>
+          <t>Base-case 12-month value</t>
+        </is>
+      </c>
+      <c r="C128" s="24">
+        <f>MAX(0,$C$126*(1+$C$94)-$C$127)</f>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Regime base: share of the log gap closed in 12 months</t>
+          <t>Bear probability</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Regime bull: probability (konglo deck)</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>0.25</v>
+          <t>Bear 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="n">
+        <v>105.2553348062861</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Regime bull: share of the log gap closed in 12 months</t>
+          <t>Base probability</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Share of today's premium kept (probability-weighted)</t>
-        </is>
-      </c>
-      <c r="C132" s="25">
-        <f>$C$126*$C$125^(1-$C$127)+$C$128*$C$125^(1-$C$129)+$C$130*$C$125^(1-$C$131)</f>
-        <v/>
+          <t>Bull probability</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TARGET PRICE (IDR) — konglo lens</t>
-        </is>
-      </c>
-      <c r="C133" s="26">
-        <f>$C$124*$C$132</f>
-        <v/>
+          <t>Bull 12-month value (engine)</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="n">
+        <v>146.8065695607831</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Expected 12-month total return</t>
-        </is>
-      </c>
-      <c r="C134" s="27">
-        <f>($C$133+$C$115)/$C$76-1</f>
+          <t>Probability-weighted 12-month value</t>
+        </is>
+      </c>
+      <c r="C134" s="24">
+        <f>$C$129*$C$130+$C$131*$C$128+$C$132*$C$133</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>Liquidity discount (limits.yaml)</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Fundamental 12-month value (after liquidity discount)</t>
+        </is>
+      </c>
+      <c r="C136" s="24">
+        <f>$C$134*(1-$C$135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Konglo lens: price / fundamental value today (engine)</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="n">
+        <v>3.888116</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Regime bear: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Regime bear: share of the log gap closed in 12 months</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Regime base: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Regime base: share of the log gap closed in 12 months</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Regime bull: probability (konglo deck)</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Regime bull: share of the log gap closed in 12 months</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Share of today's premium kept (probability-weighted)</t>
+        </is>
+      </c>
+      <c r="C144" s="25">
+        <f>$C$138*$C$137^(1-$C$139)+$C$140*$C$137^(1-$C$141)+$C$142*$C$137^(1-$C$143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TARGET PRICE (IDR) — konglo lens</t>
+        </is>
+      </c>
+      <c r="C145" s="26">
+        <f>$C$136*$C$144</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Expected 12-month total return</t>
+        </is>
+      </c>
+      <c r="C146" s="27">
+        <f>($C$145+$C$127)/$C$76-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="C135" s="28">
-        <f>IF($C$134&gt;=0.25,"BUY",IF($C$134&gt;=0.1,"ADD",IF($C$134&lt;=-0.25,"SELL",IF($C$134&lt;=-0.1,"REDUCE","HOLD"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
+      <c r="C147" s="28">
+        <f>IF($C$146&gt;=0.25,"BUY",IF($C$146&gt;=0.1,"ADD",IF($C$146&lt;=-0.25,"SELL",IF($C$146&lt;=-0.1,"REDUCE","HOLD"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
         <is>
           <t>DCF value per share vs WACC and terminal growth (engine values)</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>rows: Terminal growth (+/- pp) · columns: WACC (+/- pp)</t>
         </is>
       </c>
-      <c r="D138" s="1" t="n">
+      <c r="D150" s="1" t="n">
         <v>-0.01</v>
       </c>
-      <c r="E138" s="1" t="n">
+      <c r="E150" s="1" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F138" s="1" t="n">
+      <c r="F150" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G138" s="1" t="n">
+      <c r="G150" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="H138" s="1" t="n">
+      <c r="H150" s="1" t="n">
         <v>0.01</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="C139" s="1" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D139" s="24" t="n">
-        <v>89.138041</v>
-      </c>
-      <c r="E139" s="24" t="n">
-        <v>84.66323199999999</v>
-      </c>
-      <c r="F139" s="24" t="n">
-        <v>80.818049</v>
-      </c>
-      <c r="G139" s="24" t="n">
-        <v>77.48753600000001</v>
-      </c>
-      <c r="H139" s="24" t="n">
-        <v>74.582618</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="C140" s="1" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="D140" s="24" t="n">
-        <v>90.94046</v>
-      </c>
-      <c r="E140" s="24" t="n">
-        <v>86.098653</v>
-      </c>
-      <c r="F140" s="24" t="n">
-        <v>81.97272700000001</v>
-      </c>
-      <c r="G140" s="24" t="n">
-        <v>78.424603</v>
-      </c>
-      <c r="H140" s="24" t="n">
-        <v>75.34904899999999</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="C141" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" s="24" t="n">
-        <v>93.044764</v>
-      </c>
-      <c r="E141" s="24" t="n">
-        <v>87.75591300000001</v>
-      </c>
-      <c r="F141" s="24" t="n">
-        <v>83.29305600000001</v>
-      </c>
-      <c r="G141" s="24" t="n">
-        <v>79.487105</v>
-      </c>
-      <c r="H141" s="24" t="n">
-        <v>76.21163900000001</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="C142" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D142" s="24" t="n">
-        <v>95.533728</v>
-      </c>
-      <c r="E142" s="24" t="n">
-        <v>89.690746</v>
-      </c>
-      <c r="F142" s="24" t="n">
-        <v>84.817436</v>
-      </c>
-      <c r="G142" s="24" t="n">
-        <v>80.702034</v>
-      </c>
-      <c r="H142" s="24" t="n">
-        <v>77.18969300000001</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="C143" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D143" s="24" t="n">
-        <v>98.523436</v>
-      </c>
-      <c r="E143" s="24" t="n">
-        <v>91.97926099999999</v>
-      </c>
-      <c r="F143" s="24" t="n">
-        <v>86.597134</v>
-      </c>
-      <c r="G143" s="24" t="n">
-        <v>82.104726</v>
-      </c>
-      <c r="H143" s="24" t="n">
-        <v>78.308061</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="inlineStr">
-        <is>
-          <t>12-month value vs revenue growth and gross margin (engine values)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>rows: Gross margin (+/- pp) · columns: Revenue growth (+/- pp, every year)</t>
-        </is>
-      </c>
-      <c r="D146" s="1" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="E146" s="1" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F146" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H146" s="1" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="C147" s="1" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="D147" s="24" t="n">
-        <v>66.317224</v>
-      </c>
-      <c r="E147" s="24" t="n">
-        <v>71.9074</v>
-      </c>
-      <c r="F147" s="24" t="n">
-        <v>79.87402</v>
-      </c>
-      <c r="G147" s="24" t="n">
-        <v>91.049744</v>
-      </c>
-      <c r="H147" s="24" t="n">
-        <v>106.545277</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="C148" s="1" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D148" s="24" t="n">
-        <v>69.647479</v>
-      </c>
-      <c r="E148" s="24" t="n">
-        <v>76.102172</v>
-      </c>
-      <c r="F148" s="24" t="n">
-        <v>85.22193300000001</v>
-      </c>
-      <c r="G148" s="24" t="n">
-        <v>97.941778</v>
-      </c>
-      <c r="H148" s="24" t="n">
-        <v>115.510319</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="C149" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D149" s="24" t="n">
-        <v>72.977734</v>
-      </c>
-      <c r="E149" s="24" t="n">
-        <v>80.296944</v>
-      </c>
-      <c r="F149" s="24" t="n">
-        <v>90.569845</v>
-      </c>
-      <c r="G149" s="24" t="n">
-        <v>104.833811</v>
-      </c>
-      <c r="H149" s="24" t="n">
-        <v>124.475362</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="C150" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D150" s="24" t="n">
-        <v>76.30798900000001</v>
-      </c>
-      <c r="E150" s="24" t="n">
-        <v>84.49171699999999</v>
-      </c>
-      <c r="F150" s="24" t="n">
-        <v>95.91775699999999</v>
-      </c>
-      <c r="G150" s="24" t="n">
-        <v>111.725844</v>
-      </c>
-      <c r="H150" s="24" t="n">
-        <v>133.440405</v>
       </c>
     </row>
     <row r="151">
       <c r="C151" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D151" s="24" t="n">
+        <v>88.728056</v>
+      </c>
+      <c r="E151" s="24" t="n">
+        <v>84.27412</v>
+      </c>
+      <c r="F151" s="24" t="n">
+        <v>80.446853</v>
+      </c>
+      <c r="G151" s="24" t="n">
+        <v>77.13184099999999</v>
+      </c>
+      <c r="H151" s="24" t="n">
+        <v>74.240431</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="C152" s="1" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D152" s="24" t="n">
+        <v>90.521979</v>
+      </c>
+      <c r="E152" s="24" t="n">
+        <v>85.70278500000001</v>
+      </c>
+      <c r="F152" s="24" t="n">
+        <v>81.596102</v>
+      </c>
+      <c r="G152" s="24" t="n">
+        <v>78.064508</v>
+      </c>
+      <c r="H152" s="24" t="n">
+        <v>75.00326699999999</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="C153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="24" t="n">
+        <v>92.616347</v>
+      </c>
+      <c r="E153" s="24" t="n">
+        <v>87.352233</v>
+      </c>
+      <c r="F153" s="24" t="n">
+        <v>82.91021600000001</v>
+      </c>
+      <c r="G153" s="24" t="n">
+        <v>79.122015</v>
+      </c>
+      <c r="H153" s="24" t="n">
+        <v>75.861806</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="C154" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D154" s="24" t="n">
+        <v>95.093537</v>
+      </c>
+      <c r="E154" s="24" t="n">
+        <v>89.277931</v>
+      </c>
+      <c r="F154" s="24" t="n">
+        <v>84.427412</v>
+      </c>
+      <c r="G154" s="24" t="n">
+        <v>80.331225</v>
+      </c>
+      <c r="H154" s="24" t="n">
+        <v>76.835264</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D155" s="24" t="n">
+        <v>98.069068</v>
+      </c>
+      <c r="E155" s="24" t="n">
+        <v>91.55562</v>
+      </c>
+      <c r="F155" s="24" t="n">
+        <v>86.198707</v>
+      </c>
+      <c r="G155" s="24" t="n">
+        <v>81.727306</v>
+      </c>
+      <c r="H155" s="24" t="n">
+        <v>77.948367</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>12-month value vs revenue growth and gross margin (engine values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>rows: Gross margin (+/- pp) · columns: Revenue growth (+/- pp, every year)</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E158" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="1" t="n">
         <v>0.02</v>
       </c>
-      <c r="D151" s="24" t="n">
-        <v>79.638243</v>
-      </c>
-      <c r="E151" s="24" t="n">
-        <v>88.68648899999999</v>
-      </c>
-      <c r="F151" s="24" t="n">
-        <v>101.26567</v>
-      </c>
-      <c r="G151" s="24" t="n">
-        <v>118.617877</v>
-      </c>
-      <c r="H151" s="24" t="n">
-        <v>142.405448</v>
+      <c r="H158" s="1" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="C159" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D159" s="24" t="n">
+        <v>105.255335</v>
+      </c>
+      <c r="E159" s="24" t="n">
+        <v>108.311432</v>
+      </c>
+      <c r="F159" s="24" t="n">
+        <v>112.668458</v>
+      </c>
+      <c r="G159" s="24" t="n">
+        <v>118.782232</v>
+      </c>
+      <c r="H159" s="24" t="n">
+        <v>127.260779</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="C160" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D160" s="24" t="n">
+        <v>107.05854</v>
+      </c>
+      <c r="E160" s="24" t="n">
+        <v>110.587549</v>
+      </c>
+      <c r="F160" s="24" t="n">
+        <v>115.575487</v>
+      </c>
+      <c r="G160" s="24" t="n">
+        <v>122.534206</v>
+      </c>
+      <c r="H160" s="24" t="n">
+        <v>132.147227</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="C161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="24" t="n">
+        <v>108.861745</v>
+      </c>
+      <c r="E161" s="24" t="n">
+        <v>112.863666</v>
+      </c>
+      <c r="F161" s="24" t="n">
+        <v>118.482516</v>
+      </c>
+      <c r="G161" s="24" t="n">
+        <v>126.286181</v>
+      </c>
+      <c r="H161" s="24" t="n">
+        <v>137.033674</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="C162" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D162" s="24" t="n">
+        <v>110.664951</v>
+      </c>
+      <c r="E162" s="24" t="n">
+        <v>115.139782</v>
+      </c>
+      <c r="F162" s="24" t="n">
+        <v>121.389545</v>
+      </c>
+      <c r="G162" s="24" t="n">
+        <v>130.038155</v>
+      </c>
+      <c r="H162" s="24" t="n">
+        <v>141.920122</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="C163" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D163" s="24" t="n">
+        <v>112.468156</v>
+      </c>
+      <c r="E163" s="24" t="n">
+        <v>117.415899</v>
+      </c>
+      <c r="F163" s="24" t="n">
+        <v>124.296573</v>
+      </c>
+      <c r="G163" s="24" t="n">
+        <v>133.790129</v>
+      </c>
+      <c r="H163" s="24" t="n">
+        <v>146.80657</v>
       </c>
     </row>
   </sheetData>

--- a/models/POWER_UTILITIES.xlsx
+++ b/models/POWER_UTILITIES.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T18:55:59+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-29T23:12:35+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.05045</v>
+        <v>0.05009</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -1069,10 +1069,10 @@
         <v/>
       </c>
       <c r="H2" s="9" t="n">
-        <v>119.938334</v>
+        <v>119.772902</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>34.581938</v>
+        <v>34.539579</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>0</v>
@@ -1110,13 +1110,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>116.704817</v>
+        <v>116.543845</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>78.31366199999999</v>
+        <v>78.217111</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.002142</v>
+        <v>0.002145</v>
       </c>
     </row>
   </sheetData>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.1229591243062492</v>
+        <v>0.1231289573508711</v>
       </c>
     </row>
     <row r="92">
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="C125" s="18" t="n">
-        <v>11.510167</v>
+        <v>11.494775</v>
       </c>
     </row>
     <row r="126">
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="C137" s="15" t="n">
-        <v>229.0133708281588</v>
+        <v>229.3413938402634</v>
       </c>
     </row>
     <row r="138">
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="C140" s="15" t="n">
-        <v>240.4907830864687</v>
+        <v>240.8317881187012</v>
       </c>
     </row>
     <row r="141">
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="C144" s="18" t="n">
-        <v>10.825458</v>
+        <v>10.806589</v>
       </c>
     </row>
     <row r="145">
@@ -9033,19 +9033,19 @@
         <v>-0.01</v>
       </c>
       <c r="D158" s="24" t="n">
-        <v>69.935367</v>
+        <v>70.874217</v>
       </c>
       <c r="E158" s="24" t="n">
-        <v>58.419413</v>
+        <v>59.286199</v>
       </c>
       <c r="F158" s="24" t="n">
-        <v>47.650358</v>
+        <v>48.452479</v>
       </c>
       <c r="G158" s="24" t="n">
-        <v>37.547039</v>
+        <v>38.290625</v>
       </c>
       <c r="H158" s="24" t="n">
-        <v>28.042397</v>
+        <v>28.732617</v>
       </c>
     </row>
     <row r="159">
@@ -9053,19 +9053,19 @@
         <v>-0.005</v>
       </c>
       <c r="D159" s="24" t="n">
-        <v>70.641164</v>
+        <v>71.59335799999999</v>
       </c>
       <c r="E159" s="24" t="n">
-        <v>58.97425</v>
+        <v>59.851099</v>
       </c>
       <c r="F159" s="24" t="n">
-        <v>48.090901</v>
+        <v>48.900716</v>
       </c>
       <c r="G159" s="24" t="n">
-        <v>37.89992</v>
+        <v>38.64946</v>
       </c>
       <c r="H159" s="24" t="n">
-        <v>28.327273</v>
+        <v>29.022149</v>
       </c>
     </row>
     <row r="160">
@@ -9073,19 +9073,19 @@
         <v>0</v>
       </c>
       <c r="D160" s="24" t="n">
-        <v>71.464367</v>
+        <v>72.43283</v>
       </c>
       <c r="E160" s="24" t="n">
-        <v>59.614294</v>
+        <v>60.503223</v>
       </c>
       <c r="F160" s="24" t="n">
-        <v>48.594275</v>
+        <v>49.413203</v>
       </c>
       <c r="G160" s="24" t="n">
-        <v>38.299779</v>
+        <v>39.05629</v>
       </c>
       <c r="H160" s="24" t="n">
-        <v>28.647707</v>
+        <v>29.347979</v>
       </c>
     </row>
     <row r="161">
@@ -9093,19 +9093,19 @@
         <v>0.005</v>
       </c>
       <c r="D161" s="24" t="n">
-        <v>72.43692799999999</v>
+        <v>73.42559</v>
       </c>
       <c r="E161" s="24" t="n">
-        <v>60.360806</v>
+        <v>61.264464</v>
       </c>
       <c r="F161" s="24" t="n">
-        <v>49.174952</v>
+        <v>50.004823</v>
       </c>
       <c r="G161" s="24" t="n">
-        <v>38.756667</v>
+        <v>39.521435</v>
       </c>
       <c r="H161" s="24" t="n">
-        <v>29.0108</v>
+        <v>29.717391</v>
       </c>
     </row>
     <row r="162">
@@ -9113,19 +9113,19 @@
         <v>0.01</v>
       </c>
       <c r="D162" s="24" t="n">
-        <v>73.60355199999999</v>
+        <v>74.61784299999999</v>
       </c>
       <c r="E162" s="24" t="n">
-        <v>61.242763</v>
+        <v>62.164709</v>
       </c>
       <c r="F162" s="24" t="n">
-        <v>49.852223</v>
+        <v>50.695434</v>
       </c>
       <c r="G162" s="24" t="n">
-        <v>39.28372</v>
+        <v>40.058402</v>
       </c>
       <c r="H162" s="24" t="n">
-        <v>29.425677</v>
+        <v>30.139754</v>
       </c>
     </row>
     <row r="164">
@@ -9162,19 +9162,19 @@
         <v>-0.02</v>
       </c>
       <c r="D166" s="24" t="n">
-        <v>204.052131</v>
+        <v>203.867396</v>
       </c>
       <c r="E166" s="24" t="n">
-        <v>204.052348</v>
+        <v>203.867684</v>
       </c>
       <c r="F166" s="24" t="n">
-        <v>227.761402</v>
+        <v>228.074059</v>
       </c>
       <c r="G166" s="24" t="n">
-        <v>258.326448</v>
+        <v>258.776491</v>
       </c>
       <c r="H166" s="24" t="n">
-        <v>295.303958</v>
+        <v>295.925609</v>
       </c>
     </row>
     <row r="167">
@@ -9182,19 +9182,19 @@
         <v>-0.01</v>
       </c>
       <c r="D167" s="24" t="n">
-        <v>204.052131</v>
+        <v>203.867396</v>
       </c>
       <c r="E167" s="24" t="n">
-        <v>205.20545</v>
+        <v>205.41563</v>
       </c>
       <c r="F167" s="24" t="n">
-        <v>231.053661</v>
+        <v>231.376119</v>
       </c>
       <c r="G167" s="24" t="n">
-        <v>262.139402</v>
+        <v>262.601329</v>
       </c>
       <c r="H167" s="24" t="n">
-        <v>299.748147</v>
+        <v>300.384308</v>
       </c>
     </row>
     <row r="168">
@@ -9202,19 +9202,19 @@
         <v>0</v>
       </c>
       <c r="D168" s="24" t="n">
-        <v>204.052131</v>
+        <v>203.867396</v>
       </c>
       <c r="E168" s="24" t="n">
-        <v>208.065203</v>
+        <v>208.283522</v>
       </c>
       <c r="F168" s="24" t="n">
-        <v>234.345919</v>
+        <v>234.67818</v>
       </c>
       <c r="G168" s="24" t="n">
-        <v>265.952355</v>
+        <v>266.426166</v>
       </c>
       <c r="H168" s="24" t="n">
-        <v>304.192336</v>
+        <v>304.843008</v>
       </c>
     </row>
     <row r="169">
@@ -9222,19 +9222,19 @@
         <v>0.01</v>
       </c>
       <c r="D169" s="24" t="n">
-        <v>204.052131</v>
+        <v>203.867396</v>
       </c>
       <c r="E169" s="24" t="n">
-        <v>210.924955</v>
+        <v>211.151414</v>
       </c>
       <c r="F169" s="24" t="n">
-        <v>237.638178</v>
+        <v>237.98024</v>
       </c>
       <c r="G169" s="24" t="n">
-        <v>269.765308</v>
+        <v>270.251004</v>
       </c>
       <c r="H169" s="24" t="n">
-        <v>308.636525</v>
+        <v>309.301707</v>
       </c>
     </row>
     <row r="170">
@@ -9242,19 +9242,19 @@
         <v>0.02</v>
       </c>
       <c r="D170" s="24" t="n">
-        <v>204.052131</v>
+        <v>203.867396</v>
       </c>
       <c r="E170" s="24" t="n">
-        <v>213.784708</v>
+        <v>214.019306</v>
       </c>
       <c r="F170" s="24" t="n">
-        <v>240.930436</v>
+        <v>241.2823</v>
       </c>
       <c r="G170" s="24" t="n">
-        <v>273.578262</v>
+        <v>274.075841</v>
       </c>
       <c r="H170" s="24" t="n">
-        <v>313.080714</v>
+        <v>313.760407</v>
       </c>
     </row>
   </sheetData>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>18100</v>
+        <v>18125</v>
       </c>
     </row>
     <row r="79">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2555672767600858</v>
+        <v>0.2559202702362738</v>
       </c>
     </row>
     <row r="92">
@@ -15469,7 +15469,7 @@
         </is>
       </c>
       <c r="C113" s="18" t="n">
-        <v>15.870487</v>
+        <v>15.854827</v>
       </c>
     </row>
     <row r="114">
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="C118" s="18" t="n">
-        <v>22.834186</v>
+        <v>22.80269</v>
       </c>
     </row>
     <row r="119">
@@ -15586,7 +15586,7 @@
         </is>
       </c>
       <c r="C127" s="15" t="n">
-        <v>0.9339802975089242</v>
+        <v>0.9352703255441575</v>
       </c>
     </row>
     <row r="128">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="C130" s="15" t="n">
-        <v>105.2553348062861</v>
+        <v>105.3861498154375</v>
       </c>
     </row>
     <row r="131">
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="C133" s="15" t="n">
-        <v>146.8065695607831</v>
+        <v>147.3113773464042</v>
       </c>
     </row>
     <row r="134">
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="C137" s="18" t="n">
-        <v>3.888116</v>
+        <v>3.877952</v>
       </c>
     </row>
     <row r="138">
@@ -15830,19 +15830,19 @@
         <v>-0.01</v>
       </c>
       <c r="D151" s="24" t="n">
-        <v>88.728056</v>
+        <v>89.184899</v>
       </c>
       <c r="E151" s="24" t="n">
-        <v>84.27412</v>
+        <v>84.676474</v>
       </c>
       <c r="F151" s="24" t="n">
-        <v>80.446853</v>
+        <v>80.804665</v>
       </c>
       <c r="G151" s="24" t="n">
-        <v>77.13184099999999</v>
+        <v>77.452799</v>
       </c>
       <c r="H151" s="24" t="n">
-        <v>74.240431</v>
+        <v>74.530569</v>
       </c>
     </row>
     <row r="152">
@@ -15850,19 +15850,19 @@
         <v>-0.005</v>
       </c>
       <c r="D152" s="24" t="n">
-        <v>90.521979</v>
+        <v>91.010469</v>
       </c>
       <c r="E152" s="24" t="n">
-        <v>85.70278500000001</v>
+        <v>86.129261</v>
       </c>
       <c r="F152" s="24" t="n">
-        <v>81.596102</v>
+        <v>81.97256</v>
       </c>
       <c r="G152" s="24" t="n">
-        <v>78.064508</v>
+        <v>78.400054</v>
       </c>
       <c r="H152" s="24" t="n">
-        <v>75.00326699999999</v>
+        <v>75.304942</v>
       </c>
     </row>
     <row r="153">
@@ -15870,19 +15870,19 @@
         <v>0</v>
       </c>
       <c r="D153" s="24" t="n">
-        <v>92.616347</v>
+        <v>93.14355999999999</v>
       </c>
       <c r="E153" s="24" t="n">
-        <v>87.352233</v>
+        <v>87.80776299999999</v>
       </c>
       <c r="F153" s="24" t="n">
-        <v>82.91021600000001</v>
+        <v>83.30882699999999</v>
       </c>
       <c r="G153" s="24" t="n">
-        <v>79.122015</v>
+        <v>79.47469</v>
       </c>
       <c r="H153" s="24" t="n">
-        <v>75.861806</v>
+        <v>76.17688699999999</v>
       </c>
     </row>
     <row r="154">
@@ -15890,19 +15890,19 @@
         <v>0.005</v>
       </c>
       <c r="D154" s="24" t="n">
-        <v>95.093537</v>
+        <v>95.66902399999999</v>
       </c>
       <c r="E154" s="24" t="n">
-        <v>89.277931</v>
+        <v>89.769013</v>
       </c>
       <c r="F154" s="24" t="n">
-        <v>84.427412</v>
+        <v>84.852706</v>
       </c>
       <c r="G154" s="24" t="n">
-        <v>80.331225</v>
+        <v>80.70425299999999</v>
       </c>
       <c r="H154" s="24" t="n">
-        <v>76.835264</v>
+        <v>77.16608600000001</v>
       </c>
     </row>
     <row r="155">
@@ -15910,19 +15910,19 @@
         <v>0.01</v>
       </c>
       <c r="D155" s="24" t="n">
-        <v>98.069068</v>
+        <v>98.706091</v>
       </c>
       <c r="E155" s="24" t="n">
-        <v>91.55562</v>
+        <v>92.091027</v>
       </c>
       <c r="F155" s="24" t="n">
-        <v>86.198707</v>
+        <v>86.656655</v>
       </c>
       <c r="G155" s="24" t="n">
-        <v>81.727306</v>
+        <v>82.12485</v>
       </c>
       <c r="H155" s="24" t="n">
-        <v>77.948367</v>
+        <v>78.297895</v>
       </c>
     </row>
     <row r="157">
@@ -15959,19 +15959,19 @@
         <v>-0.02</v>
       </c>
       <c r="D159" s="24" t="n">
-        <v>105.255335</v>
+        <v>105.38615</v>
       </c>
       <c r="E159" s="24" t="n">
-        <v>108.311432</v>
+        <v>108.474541</v>
       </c>
       <c r="F159" s="24" t="n">
-        <v>112.668458</v>
+        <v>112.876604</v>
       </c>
       <c r="G159" s="24" t="n">
-        <v>118.782232</v>
+        <v>119.052859</v>
       </c>
       <c r="H159" s="24" t="n">
-        <v>127.260779</v>
+        <v>127.61766</v>
       </c>
     </row>
     <row r="160">
@@ -15979,19 +15979,19 @@
         <v>-0.01</v>
       </c>
       <c r="D160" s="24" t="n">
-        <v>107.05854</v>
+        <v>107.199601</v>
       </c>
       <c r="E160" s="24" t="n">
-        <v>110.587549</v>
+        <v>110.764717</v>
       </c>
       <c r="F160" s="24" t="n">
-        <v>115.575487</v>
+        <v>115.803003</v>
       </c>
       <c r="G160" s="24" t="n">
-        <v>122.534206</v>
+        <v>122.831584</v>
       </c>
       <c r="H160" s="24" t="n">
-        <v>132.147227</v>
+        <v>132.54109</v>
       </c>
     </row>
     <row r="161">
@@ -15999,19 +15999,19 @@
         <v>0</v>
       </c>
       <c r="D161" s="24" t="n">
-        <v>108.861745</v>
+        <v>109.013052</v>
       </c>
       <c r="E161" s="24" t="n">
-        <v>112.863666</v>
+        <v>113.054894</v>
       </c>
       <c r="F161" s="24" t="n">
-        <v>118.482516</v>
+        <v>118.729402</v>
       </c>
       <c r="G161" s="24" t="n">
-        <v>126.286181</v>
+        <v>126.610308</v>
       </c>
       <c r="H161" s="24" t="n">
-        <v>137.033674</v>
+        <v>137.464519</v>
       </c>
     </row>
     <row r="162">
@@ -16019,19 +16019,19 @@
         <v>0.01</v>
       </c>
       <c r="D162" s="24" t="n">
-        <v>110.664951</v>
+        <v>110.826503</v>
       </c>
       <c r="E162" s="24" t="n">
-        <v>115.139782</v>
+        <v>115.34507</v>
       </c>
       <c r="F162" s="24" t="n">
-        <v>121.389545</v>
+        <v>121.655801</v>
       </c>
       <c r="G162" s="24" t="n">
-        <v>130.038155</v>
+        <v>130.389033</v>
       </c>
       <c r="H162" s="24" t="n">
-        <v>141.920122</v>
+        <v>142.387948</v>
       </c>
     </row>
     <row r="163">
@@ -16039,19 +16039,19 @@
         <v>0.02</v>
       </c>
       <c r="D163" s="24" t="n">
-        <v>112.468156</v>
+        <v>112.639954</v>
       </c>
       <c r="E163" s="24" t="n">
-        <v>117.415899</v>
+        <v>117.635247</v>
       </c>
       <c r="F163" s="24" t="n">
-        <v>124.296573</v>
+        <v>124.5822</v>
       </c>
       <c r="G163" s="24" t="n">
-        <v>133.790129</v>
+        <v>134.167758</v>
       </c>
       <c r="H163" s="24" t="n">
-        <v>146.80657</v>
+        <v>147.311377</v>
       </c>
     </row>
   </sheetData>

--- a/models/POWER_UTILITIES.xlsx
+++ b/models/POWER_UTILITIES.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29T23:12:35+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
+          <t>Generated 2026-10-30T04:49:03+07:00 by the coverage engine. The engine (scripts/cov_engine.py) is the source of truth; this workbook is a live rendering of it.</t>
         </is>
       </c>
     </row>
@@ -1110,13 +1110,13 @@
         <v/>
       </c>
       <c r="H3" s="9" t="n">
-        <v>116.543845</v>
+        <v>104.460995</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>78.217111</v>
+        <v>69.809945</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.002145</v>
+        <v>0.003829</v>
       </c>
     </row>
   </sheetData>
@@ -9286,7 +9286,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-29 · data 2026-10-27</t>
+          <t>Units: USD m; per-share in USD unless marked IDR. Model asof 2026-10-30 · data 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.235</v>
+        <v>0.22</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.235</v>
+        <v>0.225</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.235</v>
+        <v>0.23</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>0.235</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.05</v>
+        <v>0.85</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0.75</v>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="G21" s="13" t="n">
-        <v>205.4</v>
+        <v>331.7</v>
       </c>
       <c r="H21" s="13" t="n">
         <v>100</v>
@@ -10223,64 +10223,64 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -12076,7 +12076,7 @@
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="15" t="n"/>
       <c r="F46" s="15" t="n">
-        <v>0.0004713384185926629</v>
+        <v>0.000470683850452992</v>
       </c>
       <c r="G46" s="16">
         <f>(MAX(G45,0)*G24)</f>
@@ -14648,7 +14648,7 @@
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n">
-        <v>0.4860440631807598</v>
+        <v>0.4853690726735478</v>
       </c>
       <c r="G72" s="17">
         <f>IF(G45=0,0,G46/G45)</f>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="C76" s="15" t="n">
-        <v>436</v>
+        <v>362</v>
       </c>
     </row>
     <row r="77">
@@ -14914,7 +14914,7 @@
         </is>
       </c>
       <c r="C83" s="13" t="n">
-        <v>755.209121</v>
+        <v>802.812121</v>
       </c>
     </row>
     <row r="84">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="C91" s="21" t="n">
-        <v>0.2559202702362738</v>
+        <v>0.30823546359949</v>
       </c>
     </row>
     <row r="92">
@@ -15148,61 +15148,61 @@
         <v>0</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>0.673511</v>
+        <v>0.670773</v>
       </c>
       <c r="I101" s="12" t="n">
-        <v>1.672827</v>
+        <v>1.670089</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>2.67488</v>
+        <v>2.672142</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>3.674196</v>
+        <v>3.671458</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>4.673511</v>
+        <v>4.670773</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>5.672827</v>
+        <v>5.670089</v>
       </c>
       <c r="N101" s="12" t="n">
-        <v>6.67488</v>
+        <v>6.672142</v>
       </c>
       <c r="O101" s="12" t="n">
-        <v>7.674196</v>
+        <v>7.671458</v>
       </c>
       <c r="P101" s="12" t="n">
-        <v>8.673511</v>
+        <v>8.670773000000001</v>
       </c>
       <c r="Q101" s="12" t="n">
-        <v>9.672827</v>
+        <v>9.670089000000001</v>
       </c>
       <c r="R101" s="12" t="n">
-        <v>10.67488</v>
+        <v>10.672142</v>
       </c>
       <c r="S101" s="12" t="n">
-        <v>11.674196</v>
+        <v>11.671458</v>
       </c>
       <c r="T101" s="12" t="n">
-        <v>12.673511</v>
+        <v>12.670773</v>
       </c>
       <c r="U101" s="12" t="n">
-        <v>13.672827</v>
+        <v>13.670089</v>
       </c>
       <c r="V101" s="12" t="n">
-        <v>14.67488</v>
+        <v>14.672142</v>
       </c>
       <c r="W101" s="12" t="n">
-        <v>15.674196</v>
+        <v>15.671458</v>
       </c>
       <c r="X101" s="12" t="n">
-        <v>16.673511</v>
+        <v>16.670773</v>
       </c>
       <c r="Y101" s="12" t="n">
-        <v>17.672827</v>
+        <v>17.670089</v>
       </c>
       <c r="Z101" s="12" t="n">
-        <v>18.67488</v>
+        <v>18.672142</v>
       </c>
     </row>
     <row r="102">
@@ -15397,7 +15397,7 @@
         </is>
       </c>
       <c r="C105" s="20" t="n">
-        <v>19.173169</v>
+        <v>19.170431</v>
       </c>
     </row>
     <row r="106">
@@ -15479,7 +15479,7 @@
         </is>
       </c>
       <c r="C114" s="13" t="n">
-        <v>17.099855</v>
+        <v>31.923456</v>
       </c>
     </row>
     <row r="115">
@@ -15496,7 +15496,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>P/E</t>
+          <t>Dividend yield</t>
         </is>
       </c>
     </row>
@@ -15506,8 +15506,8 @@
           <t>Target multiple (peer median)</t>
         </is>
       </c>
-      <c r="C118" s="18" t="n">
-        <v>22.80269</v>
+      <c r="C118" s="4" t="n">
+        <v>0.010024</v>
       </c>
     </row>
     <row r="119">
@@ -15517,17 +15517,17 @@
         </is>
       </c>
       <c r="C119" s="13" t="n">
-        <v>70.49733999999999</v>
+        <v>7.6e-05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Value per share (IDR) — P/E</t>
+          <t>Value per share (IDR) — Dividend yield</t>
         </is>
       </c>
       <c r="C120" s="24">
-        <f>MAX(0,$C$118*$C$119/$C$77*$C$85*$C$78)</f>
+        <f>MAX(0,$C$119/$C$118*$C$78)</f>
         <v/>
       </c>
     </row>
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="124">
@@ -15555,13 +15555,13 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Weight: P/E</t>
+          <t>Weight: Dividend yield</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
@@ -15586,7 +15586,7 @@
         </is>
       </c>
       <c r="C127" s="15" t="n">
-        <v>0.9352703255441575</v>
+        <v>1.386163320976524</v>
       </c>
     </row>
     <row r="128">
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="C130" s="15" t="n">
-        <v>105.3861498154375</v>
+        <v>109.3541650245479</v>
       </c>
     </row>
     <row r="131">
@@ -15647,7 +15647,7 @@
         </is>
       </c>
       <c r="C133" s="15" t="n">
-        <v>147.3113773464042</v>
+        <v>159.1730284120069</v>
       </c>
     </row>
     <row r="134">
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="C137" s="18" t="n">
-        <v>3.877952</v>
+        <v>3.02899</v>
       </c>
     </row>
     <row r="138">
@@ -15830,19 +15830,19 @@
         <v>-0.01</v>
       </c>
       <c r="D151" s="24" t="n">
-        <v>89.184899</v>
+        <v>98.293525</v>
       </c>
       <c r="E151" s="24" t="n">
-        <v>84.676474</v>
+        <v>93.766702</v>
       </c>
       <c r="F151" s="24" t="n">
-        <v>80.804665</v>
+        <v>89.880127</v>
       </c>
       <c r="G151" s="24" t="n">
-        <v>77.452799</v>
+        <v>86.516283</v>
       </c>
       <c r="H151" s="24" t="n">
-        <v>74.530569</v>
+        <v>83.58425099999999</v>
       </c>
     </row>
     <row r="152">
@@ -15850,19 +15850,19 @@
         <v>-0.005</v>
       </c>
       <c r="D152" s="24" t="n">
-        <v>91.010469</v>
+        <v>100.131083</v>
       </c>
       <c r="E152" s="24" t="n">
-        <v>86.129261</v>
+        <v>95.22861899999999</v>
       </c>
       <c r="F152" s="24" t="n">
-        <v>81.97256</v>
+        <v>91.055074</v>
       </c>
       <c r="G152" s="24" t="n">
-        <v>78.400054</v>
+        <v>87.469054</v>
       </c>
       <c r="H152" s="24" t="n">
-        <v>75.304942</v>
+        <v>84.36298600000001</v>
       </c>
     </row>
     <row r="153">
@@ -15870,19 +15870,19 @@
         <v>0</v>
       </c>
       <c r="D153" s="24" t="n">
-        <v>93.14355999999999</v>
+        <v>102.27889</v>
       </c>
       <c r="E153" s="24" t="n">
-        <v>87.80776299999999</v>
+        <v>96.918147</v>
       </c>
       <c r="F153" s="24" t="n">
-        <v>83.30882699999999</v>
+        <v>92.39974100000001</v>
       </c>
       <c r="G153" s="24" t="n">
-        <v>79.47469</v>
+        <v>88.55018200000001</v>
       </c>
       <c r="H153" s="24" t="n">
-        <v>76.17688699999999</v>
+        <v>85.240011</v>
       </c>
     </row>
     <row r="154">
@@ -15890,19 +15890,19 @@
         <v>0.005</v>
       </c>
       <c r="D154" s="24" t="n">
-        <v>95.66902399999999</v>
+        <v>104.822763</v>
       </c>
       <c r="E154" s="24" t="n">
-        <v>89.769013</v>
+        <v>98.892931</v>
       </c>
       <c r="F154" s="24" t="n">
-        <v>84.852706</v>
+        <v>93.953766</v>
       </c>
       <c r="G154" s="24" t="n">
-        <v>80.70425299999999</v>
+        <v>89.787477</v>
       </c>
       <c r="H154" s="24" t="n">
-        <v>77.16608600000001</v>
+        <v>86.23518799999999</v>
       </c>
     </row>
     <row r="155">
@@ -15910,19 +15910,19 @@
         <v>0.01</v>
       </c>
       <c r="D155" s="24" t="n">
-        <v>98.706091</v>
+        <v>107.883384</v>
       </c>
       <c r="E155" s="24" t="n">
-        <v>92.091027</v>
+        <v>101.231876</v>
       </c>
       <c r="F155" s="24" t="n">
-        <v>86.656655</v>
+        <v>95.770168</v>
       </c>
       <c r="G155" s="24" t="n">
-        <v>82.12485</v>
+        <v>91.217412</v>
       </c>
       <c r="H155" s="24" t="n">
-        <v>78.297895</v>
+        <v>87.374117</v>
       </c>
     </row>
     <row r="157">
@@ -15959,19 +15959,19 @@
         <v>-0.02</v>
       </c>
       <c r="D159" s="24" t="n">
-        <v>105.38615</v>
+        <v>109.354165</v>
       </c>
       <c r="E159" s="24" t="n">
-        <v>108.474541</v>
+        <v>112.89691</v>
       </c>
       <c r="F159" s="24" t="n">
-        <v>112.876604</v>
+        <v>117.879927</v>
       </c>
       <c r="G159" s="24" t="n">
-        <v>119.052859</v>
+        <v>124.808288</v>
       </c>
       <c r="H159" s="24" t="n">
-        <v>127.61766</v>
+        <v>134.355814</v>
       </c>
     </row>
     <row r="160">
@@ -15979,19 +15979,19 @@
         <v>-0.01</v>
       </c>
       <c r="D160" s="24" t="n">
-        <v>107.199601</v>
+        <v>112.09575</v>
       </c>
       <c r="E160" s="24" t="n">
-        <v>110.764717</v>
+        <v>116.174392</v>
       </c>
       <c r="F160" s="24" t="n">
-        <v>115.803003</v>
+        <v>121.868178</v>
       </c>
       <c r="G160" s="24" t="n">
-        <v>122.831584</v>
+        <v>129.744261</v>
       </c>
       <c r="H160" s="24" t="n">
-        <v>132.54109</v>
+        <v>140.560118</v>
       </c>
     </row>
     <row r="161">
@@ -15999,19 +15999,19 @@
         <v>0</v>
       </c>
       <c r="D161" s="24" t="n">
-        <v>109.013052</v>
+        <v>114.837334</v>
       </c>
       <c r="E161" s="24" t="n">
-        <v>113.054894</v>
+        <v>119.451874</v>
       </c>
       <c r="F161" s="24" t="n">
-        <v>118.729402</v>
+        <v>125.856429</v>
       </c>
       <c r="G161" s="24" t="n">
-        <v>126.610308</v>
+        <v>134.680234</v>
       </c>
       <c r="H161" s="24" t="n">
-        <v>137.464519</v>
+        <v>146.764421</v>
       </c>
     </row>
     <row r="162">
@@ -16019,19 +16019,19 @@
         <v>0.01</v>
       </c>
       <c r="D162" s="24" t="n">
-        <v>110.826503</v>
+        <v>117.578919</v>
       </c>
       <c r="E162" s="24" t="n">
-        <v>115.34507</v>
+        <v>122.729356</v>
       </c>
       <c r="F162" s="24" t="n">
-        <v>121.655801</v>
+        <v>129.84468</v>
       </c>
       <c r="G162" s="24" t="n">
-        <v>130.389033</v>
+        <v>139.616208</v>
       </c>
       <c r="H162" s="24" t="n">
-        <v>142.387948</v>
+        <v>152.968725</v>
       </c>
     </row>
     <row r="163">
@@ -16039,19 +16039,19 @@
         <v>0.02</v>
       </c>
       <c r="D163" s="24" t="n">
-        <v>112.639954</v>
+        <v>120.320503</v>
       </c>
       <c r="E163" s="24" t="n">
-        <v>117.635247</v>
+        <v>126.006838</v>
       </c>
       <c r="F163" s="24" t="n">
-        <v>124.5822</v>
+        <v>133.832931</v>
       </c>
       <c r="G163" s="24" t="n">
-        <v>134.167758</v>
+        <v>144.552181</v>
       </c>
       <c r="H163" s="24" t="n">
-        <v>147.311377</v>
+        <v>159.173028</v>
       </c>
     </row>
   </sheetData>
